--- a/new-info44/web.xlsx
+++ b/new-info44/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21585" windowHeight="10050"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="14" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
   <si>
     <t>domain</t>
   </si>
@@ -42,85 +42,124 @@
     <t>color2</t>
   </si>
   <si>
-    <t>play.radiciflorous.com</t>
+    <t>gossamer.fun</t>
+  </si>
+  <si>
+    <t>#def0f9</t>
+  </si>
+  <si>
+    <t>#4167b1</t>
+  </si>
+  <si>
+    <t>turbinate.fun</t>
+  </si>
+  <si>
+    <t>#f8e9a1</t>
+  </si>
+  <si>
+    <t>#d62828</t>
+  </si>
+  <si>
+    <t>frondesc.fun</t>
+  </si>
+  <si>
+    <t>#f9f0ed</t>
+  </si>
+  <si>
+    <t>#e58889</t>
+  </si>
+  <si>
+    <t>gaberdine.cloud</t>
+  </si>
+  <si>
+    <t>#ebdec6</t>
+  </si>
+  <si>
+    <t>#b57743</t>
+  </si>
+  <si>
+    <t>sequester.cloud</t>
+  </si>
+  <si>
+    <t>#f7ece7</t>
+  </si>
+  <si>
+    <t>#a61b29</t>
+  </si>
+  <si>
+    <t>spuddles.fun</t>
+  </si>
+  <si>
+    <t>#707899</t>
+  </si>
+  <si>
+    <t>moilfuns.fun</t>
+  </si>
+  <si>
+    <t>#70c588</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>nimbiferous.com</t>
+  </si>
+  <si>
+    <t>#c4b091</t>
+  </si>
+  <si>
+    <t>daggledown.com</t>
+  </si>
+  <si>
+    <t>#fac03d</t>
+  </si>
+  <si>
+    <t>quodlibets.com</t>
+  </si>
+  <si>
+    <t>#aa9649</t>
+  </si>
+  <si>
+    <t>obganiate.com</t>
+  </si>
+  <si>
+    <t>#b65458</t>
+  </si>
+  <si>
+    <t>quagmiry.com</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>play.mettas.site</t>
+  </si>
+  <si>
+    <t>#957aa9</t>
+  </si>
+  <si>
+    <t>sec.mettas.site</t>
+  </si>
+  <si>
+    <t>#33325d</t>
+  </si>
+  <si>
+    <t>play.derives.cloud</t>
+  </si>
+  <si>
+    <t>#4189b3</t>
+  </si>
+  <si>
+    <t>sec.derives.cloud</t>
   </si>
   <si>
     <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>sec.radiciflorous.com</t>
-  </si>
-  <si>
-    <t>#33325d</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>nimbiferous.com</t>
-  </si>
-  <si>
-    <t>#c4b091</t>
-  </si>
-  <si>
-    <t>daggledown.com</t>
-  </si>
-  <si>
-    <t>#fac03d</t>
-  </si>
-  <si>
-    <t>quodlibets.com</t>
-  </si>
-  <si>
-    <t>#aa9649</t>
-  </si>
-  <si>
-    <t>obganiate.com</t>
-  </si>
-  <si>
-    <t>#b65458</t>
-  </si>
-  <si>
-    <t>quagmiry.com</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
-  </si>
-  <si>
-    <t>play.mettas.site</t>
-  </si>
-  <si>
-    <t>#957aa9</t>
-  </si>
-  <si>
-    <t>sec.mettas.site</t>
-  </si>
-  <si>
-    <t>play.derives.cloud</t>
-  </si>
-  <si>
-    <t>#4189b3</t>
-  </si>
-  <si>
-    <t>sec.derives.cloud</t>
   </si>
   <si>
     <t>lagoonsea.com</t>
@@ -292,7 +331,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="42">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -423,6 +462,33 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color rgb="FF1450B8"/>
       <name val="Helvetica"/>
@@ -572,7 +638,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="58">
+  <fills count="67">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -713,7 +779,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAFCD53"/>
+        <fgColor rgb="FFDEF0F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4167B1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8E9A1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD62828"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F0ED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE58889"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBDEC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB57743"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7ECE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA61B29"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1064,152 +1184,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1320,28 +1440,49 @@
     <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1749,57 +1890,81 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" ht="16.5" spans="1:7">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="42"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="C2" s="42" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:7">
       <c r="A3" s="40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="42"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
+        <v>7</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:7">
+      <c r="A4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
+      <c r="A6" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="46" t="s">
-        <v>8</v>
+      <c r="F16" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="6:7">
-      <c r="F17" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="47" t="s">
-        <v>10</v>
+      <c r="F17" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="54" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
     <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
-    <hyperlink ref="A6" r:id="rId3"/>
-    <hyperlink ref="A2" r:id="rId4" display="play.radiciflorous.com" tooltip="http://radiciflorous.com"/>
-    <hyperlink ref="A3" r:id="rId4" display="sec.radiciflorous.com" tooltip="http://radiciflorous.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1820,24 +1985,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="24" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2">
@@ -1849,10 +2014,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="24" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3">
@@ -1864,10 +2029,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="24" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4">
@@ -1879,10 +2044,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="24" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5">
@@ -1894,10 +2059,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="24" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C6" s="35"/>
       <c r="D6">
@@ -1943,24 +2108,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="26" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2">
@@ -1972,10 +2137,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="26" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3">
@@ -1987,10 +2152,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="30" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4">
@@ -2002,10 +2167,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5">
@@ -2048,24 +2213,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="17" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2">
@@ -2077,10 +2242,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="17" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3">
@@ -2092,10 +2257,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4">
@@ -2107,10 +2272,10 @@
     </row>
     <row r="5" ht="15" spans="1:6">
       <c r="A5" s="17" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5">
@@ -2123,10 +2288,10 @@
     </row>
     <row r="6" ht="15" spans="1:6">
       <c r="A6" s="24" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6">
@@ -2186,7 +2351,7 @@
   <sheetData>
     <row r="1" ht="31.5" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2197,141 +2362,141 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="83" customHeight="1" spans="1:10">
       <c r="A5" s="5" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="J5" s="7"/>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:10">
       <c r="A6" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" ht="75" customHeight="1" spans="1:10">
       <c r="A7" s="9" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" ht="97" customHeight="1" spans="1:10">
@@ -2352,7 +2517,7 @@
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
     </row>
-    <row r="12" ht="15.75" spans="1:10">
+    <row r="12" spans="1:10">
       <c r="A12" s="14"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>

--- a/new-info44/web.xlsx
+++ b/new-info44/web.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>domain</t>
   </si>
@@ -42,61 +42,31 @@
     <t>color2</t>
   </si>
   <si>
-    <t>gossamer.fun</t>
-  </si>
-  <si>
-    <t>#def0f9</t>
-  </si>
-  <si>
-    <t>#4167b1</t>
-  </si>
-  <si>
-    <t>turbinate.fun</t>
-  </si>
-  <si>
-    <t>#f8e9a1</t>
-  </si>
-  <si>
-    <t>#d62828</t>
-  </si>
-  <si>
-    <t>frondesc.fun</t>
-  </si>
-  <si>
-    <t>#f9f0ed</t>
-  </si>
-  <si>
-    <t>#e58889</t>
-  </si>
-  <si>
-    <t>gaberdine.cloud</t>
-  </si>
-  <si>
-    <t>#ebdec6</t>
-  </si>
-  <si>
-    <t>#b57743</t>
-  </si>
-  <si>
-    <t>sequester.cloud</t>
-  </si>
-  <si>
-    <t>#f7ece7</t>
-  </si>
-  <si>
-    <t>#a61b29</t>
-  </si>
-  <si>
-    <t>spuddles.fun</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>moilfuns.fun</t>
-  </si>
-  <si>
-    <t>#70c588</t>
+    <t>read.frondesc.fun</t>
+  </si>
+  <si>
+    <t>#c6e6e8</t>
+  </si>
+  <si>
+    <t>#36435a</t>
+  </si>
+  <si>
+    <t>sec.frondesc.fun</t>
+  </si>
+  <si>
+    <t>#fdf4e3</t>
+  </si>
+  <si>
+    <t>#7c8d99</t>
+  </si>
+  <si>
+    <t>info.frondesc.fun</t>
+  </si>
+  <si>
+    <t>#e1e6e9</t>
+  </si>
+  <si>
+    <t>#a35e5e</t>
   </si>
   <si>
     <t>color1</t>
@@ -331,7 +301,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="38">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -462,33 +432,6 @@
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
       <sz val="10"/>
       <color rgb="FF1450B8"/>
       <name val="Helvetica"/>
@@ -779,37 +722,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEF0F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4167B1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8E9A1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD62828"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9F0ED"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE58889"/>
+        <fgColor rgb="FFC6E6E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36435A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7C8D99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1E6E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA35E5E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1184,148 +1127,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="38" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="38" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1440,43 +1383,43 @@
     <xf numFmtId="0" fontId="10" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1890,7 +1833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:7">
+    <row r="2" spans="1:7">
       <c r="A2" s="40" t="s">
         <v>3</v>
       </c>
@@ -1901,7 +1844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3" s="40" t="s">
         <v>6</v>
       </c>
@@ -1912,7 +1855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:7">
+    <row r="4" spans="1:7">
       <c r="A4" s="40" t="s">
         <v>9</v>
       </c>
@@ -1924,48 +1867,24 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>14</v>
-      </c>
+      <c r="A5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>17</v>
-      </c>
+      <c r="A6" s="47"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="51"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="F16" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="53" t="s">
-        <v>19</v>
-      </c>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="6:7">
-      <c r="F17" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="54" t="s">
-        <v>21</v>
-      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="54"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F16" r:id="rId1" display="spuddles.fun"/>
-    <hyperlink ref="F17" r:id="rId2" display="moilfuns.fun"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1985,24 +1904,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="24" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2">
@@ -2014,10 +1933,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="24" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3">
@@ -2029,10 +1948,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="24" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4">
@@ -2044,10 +1963,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="24" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C5" s="35"/>
       <c r="D5">
@@ -2059,10 +1978,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="24" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C6" s="35"/>
       <c r="D6">
@@ -2108,24 +2027,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="26" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C2" s="28"/>
       <c r="D2">
@@ -2137,10 +2056,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="26" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3">
@@ -2152,10 +2071,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="30" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4">
@@ -2167,10 +2086,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5">
@@ -2213,24 +2132,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="17" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2">
@@ -2242,10 +2161,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="17" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3">
@@ -2257,10 +2176,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4">
@@ -2272,10 +2191,10 @@
     </row>
     <row r="5" ht="15" spans="1:6">
       <c r="A5" s="17" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5">
@@ -2288,10 +2207,10 @@
     </row>
     <row r="6" ht="15" spans="1:6">
       <c r="A6" s="24" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6">
@@ -2351,7 +2270,7 @@
   <sheetData>
     <row r="1" ht="31.5" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2362,141 +2281,141 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="83" customHeight="1" spans="1:10">
       <c r="A5" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="J5" s="7"/>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:10">
       <c r="A6" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="75" customHeight="1" spans="1:10">
       <c r="A7" s="9" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" ht="75" customHeight="1" spans="1:10">
       <c r="A8" s="10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="70" customHeight="1" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="97" customHeight="1" spans="1:10">

--- a/new-info44/web.xlsx
+++ b/new-info44/web.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="16740" windowHeight="11775"/>
+    <workbookView windowWidth="14475" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="15" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="13" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>domain</t>
   </si>
@@ -40,31 +41,25 @@
     <t>color2</t>
   </si>
   <si>
-    <t>read.turbinate.fun</t>
-  </si>
-  <si>
-    <t>#c6e6e8</t>
-  </si>
-  <si>
-    <t>#373834</t>
-  </si>
-  <si>
-    <t>sec.turbinate.fun</t>
-  </si>
-  <si>
-    <t>#e3e3e5</t>
-  </si>
-  <si>
-    <t>#707899</t>
-  </si>
-  <si>
-    <t>info.turbinate.fun</t>
-  </si>
-  <si>
-    <t>#f5f4f7</t>
-  </si>
-  <si>
-    <t>#2c9678</t>
+    <t>date</t>
+  </si>
+  <si>
+    <t>read.gaberdine.cloud</t>
+  </si>
+  <si>
+    <t>#f9f3e0</t>
+  </si>
+  <si>
+    <t>#1660ab</t>
+  </si>
+  <si>
+    <t>sec.gaberdine.cloud</t>
+  </si>
+  <si>
+    <t>#e2e7bf</t>
+  </si>
+  <si>
+    <t>#2b313f</t>
   </si>
   <si>
     <t>color1</t>
@@ -76,47 +71,78 @@
     <t>json</t>
   </si>
   <si>
-    <t>haberdasher.cloud</t>
-  </si>
-  <si>
-    <t>#fb9966</t>
-  </si>
-  <si>
-    <t>melancholy.cloud</t>
-  </si>
-  <si>
-    <t>#afcd53</t>
-  </si>
-  <si>
-    <t>insulary.fun</t>
-  </si>
-  <si>
-    <t>#ed6d46</t>
-  </si>
-  <si>
-    <t>vapourous.fun</t>
-  </si>
-  <si>
-    <t>#7d929f</t>
-  </si>
-  <si>
-    <t>unsdgaction.com</t>
-  </si>
-  <si>
-    <t>#ddbb99</t>
+    <t>play.sepulchre.cloud</t>
+  </si>
+  <si>
+    <t>#e07563</t>
+  </si>
+  <si>
+    <t>sec.sepulchre.cloud</t>
+  </si>
+  <si>
+    <t>#41bbcb</t>
+  </si>
+  <si>
+    <t>play.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#f53d93</t>
+  </si>
+  <si>
+    <t>sec.kaleidos.fun</t>
+  </si>
+  <si>
+    <t>#ff978a</t>
+  </si>
+  <si>
+    <t>play.fervid.site</t>
+  </si>
+  <si>
+    <t>#6ae966</t>
+  </si>
+  <si>
+    <t>sec.fervid.site</t>
+  </si>
+  <si>
+    <t>#a515f9</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>周日</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -125,15 +151,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -147,6 +167,78 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -155,36 +247,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -321,7 +383,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,67 +392,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFB9966"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7D929F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFCD53"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED6D46"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDBB99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E6E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF373834"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3E3E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF707899"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F4F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2C9678"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF53D93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE63946"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF978A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AE966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA515F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE07563"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41BBCB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F3E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1660AB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E7BF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B313F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,208 +758,216 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1282,10 +1358,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="27.75" customWidth="1"/>
+    <col min="4" max="4" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1298,201 +1375,205 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="19" t="s">
         <v>8</v>
       </c>
+      <c r="C3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="17"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="D21" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3" tooltip="http://seacalmy.com"/>
+    <hyperlink ref="A5" r:id="rId3" tooltip="http://seacalmy.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1502,8 +1583,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.375" customWidth="1"/>
   </cols>
@@ -1513,91 +1594,119 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="13"/>
+      <c r="D3" s="13">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>14</v>
+      <c r="E3" s="13">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>14</v>
-      </c>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>14</v>
-      </c>
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
+    <hyperlink ref="A8" r:id="rId1"/>
+    <hyperlink ref="A9" r:id="rId2"/>
+    <hyperlink ref="A10" r:id="rId3"/>
+    <hyperlink ref="A11" r:id="rId4"/>
+    <hyperlink ref="A6" r:id="rId5" tooltip="http://gravecaller.com"/>
+    <hyperlink ref="A7" r:id="rId5" tooltip="http://gravecaller.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1607,108 +1716,159 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7">
+        <v>16</v>
+      </c>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="8" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="7">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>16</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
-  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="E2" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/new-info44/web.xlsx
+++ b/new-info44/web.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info44\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14475" windowHeight="10890"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>domain</t>
   </si>
@@ -44,22 +49,13 @@
     <t>date</t>
   </si>
   <si>
-    <t>read.gaberdine.cloud</t>
-  </si>
-  <si>
-    <t>#f9f3e0</t>
-  </si>
-  <si>
-    <t>#1660ab</t>
-  </si>
-  <si>
-    <t>sec.gaberdine.cloud</t>
-  </si>
-  <si>
-    <t>#e2e7bf</t>
-  </si>
-  <si>
-    <t>#2b313f</t>
+    <t>turbinate.fun</t>
+  </si>
+  <si>
+    <t>#f8e9a1</t>
+  </si>
+  <si>
+    <t>#d62828</t>
   </si>
   <si>
     <t>color1</t>
@@ -142,7 +138,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -196,11 +192,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Microsoft YaHei"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -209,6 +211,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
@@ -440,13 +449,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9F3E0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1660AB"/>
+        <fgColor rgb="FFF8E9A1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD62828"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,28 +767,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -788,118 +788,127 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -931,9 +940,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -946,28 +952,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1379,8 +1388,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="11" t="s">
+    <row r="2" ht="16.5" spans="1:8">
+      <c r="A2" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -1392,15 +1401,9 @@
       <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>9</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:8">
@@ -1436,9 +1439,9 @@
       <c r="H7" s="23"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -1572,7 +1575,6 @@
   <hyperlinks>
     <hyperlink ref="F16" r:id="rId1"/>
     <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="A4" r:id="rId3" tooltip="http://seacalmy.com"/>
     <hyperlink ref="A5" r:id="rId3" tooltip="http://seacalmy.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1594,75 +1596,75 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13">
-        <v>1</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12">
+        <v>2</v>
+      </c>
+      <c r="E3" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13">
-        <v>2</v>
-      </c>
-      <c r="E3" s="13">
-        <v>4</v>
-      </c>
-    </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4"/>
@@ -1679,25 +1681,25 @@
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1727,24 +1729,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7">
@@ -1757,10 +1759,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="7">
@@ -1773,10 +1775,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="7">
@@ -1789,10 +1791,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="7">
@@ -1841,28 +1843,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:8">
